--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133516366</v>
+        <v>133515300</v>
       </c>
       <c r="B2" t="n">
-        <v>58260</v>
+        <v>75354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>6427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Torsebrobruk NV, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445056</v>
+        <v>444945</v>
       </c>
       <c r="R2" t="n">
-        <v>6219008</v>
+        <v>6218857</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -762,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133515359</v>
+        <v>133515346</v>
       </c>
       <c r="B3" t="n">
-        <v>75326</v>
+        <v>75354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>6427</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -878,6 +874,416 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133515359</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75340</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Torsebrobruk NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>444984</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6218888</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Färlöv</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133515342</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Torsebrobruk NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>444984</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6218888</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Färlöv</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133515326</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99504</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Torsebrobruk NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>444945</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6218857</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Färlöv</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133516366</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58260</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Torsebrobruk NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>445056</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6219008</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Färlöv</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133515300</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133515346</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133515359</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133516366</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133515342</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,8 +1314,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133515326</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133515300</v>
+        <v>136127731</v>
       </c>
       <c r="B2" t="n">
-        <v>75354</v>
+        <v>96519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6427</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Glansfläck</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Diarthonis spadicea</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Leight.) Frisch &amp; al.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Torsebrobruk NV, Sk</t>
+          <t>Stubbarp, Stubbarp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444945</v>
+        <v>445025</v>
       </c>
       <c r="R2" t="n">
-        <v>6218857</v>
+        <v>6218815</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,34 +759,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Ingvarsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Ingvarsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133515300</t>
+          <t>https://artportalen.se/Sighting/136127731</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133515346</v>
+        <v>136127743</v>
       </c>
       <c r="B3" t="n">
-        <v>75354</v>
+        <v>96519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,40 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6427</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Glansfläck</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Diarthonis spadicea</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Leight.) Frisch &amp; al.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Torsebrobruk NV, Sk</t>
+          <t>Stubbarp, Stubbarp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444984</v>
+        <v>445045</v>
       </c>
       <c r="R3" t="n">
-        <v>6218888</v>
+        <v>6218785</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,34 +861,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Ingvarsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Ingvarsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133515346</t>
+          <t>https://artportalen.se/Sighting/136127743</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133515359</v>
+        <v>133515300</v>
       </c>
       <c r="B4" t="n">
-        <v>75340</v>
+        <v>75354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>6427</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444984</v>
+        <v>444945</v>
       </c>
       <c r="R4" t="n">
-        <v>6218888</v>
+        <v>6218857</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
@@ -992,59 +984,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133515359</t>
+          <t>https://artportalen.se/Sighting/133515300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133516366</v>
+        <v>133515346</v>
       </c>
       <c r="B5" t="n">
-        <v>58260</v>
+        <v>75354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>6427</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Torsebrobruk NV, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445056</v>
+        <v>444984</v>
       </c>
       <c r="R5" t="n">
-        <v>6219008</v>
+        <v>6218888</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,6 +1072,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1102,16 +1090,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133516366</t>
+          <t>https://artportalen.se/Sighting/133515346</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133515342</v>
+        <v>133515359</v>
       </c>
       <c r="B6" t="n">
-        <v>106199</v>
+        <v>75340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,27 +1107,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221154</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
@@ -1209,55 +1196,59 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133515342</t>
+          <t>https://artportalen.se/Sighting/133515359</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133515326</v>
+        <v>133516366</v>
       </c>
       <c r="B7" t="n">
-        <v>99504</v>
+        <v>58260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222857</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Torsebrobruk NV, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444945</v>
+        <v>445056</v>
       </c>
       <c r="R7" t="n">
-        <v>6218857</v>
+        <v>6219008</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1298,7 +1289,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,6 +1305,220 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133516366</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133515342</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106199</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Torsebrobruk NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>444984</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6218888</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Färlöv</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133515342</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133515326</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99504</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Torsebrobruk NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>444945</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6218857</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Färlöv</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133515326</t>
         </is>
@@ -1328,6 +1532,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127731</v>
       </c>
       <c r="B2" t="n">
-        <v>96519</v>
+        <v>96520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136127743</v>
       </c>
       <c r="B3" t="n">
-        <v>96519</v>
+        <v>96520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127731</v>
       </c>
       <c r="B2" t="n">
-        <v>96520</v>
+        <v>96521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136127743</v>
       </c>
       <c r="B3" t="n">
-        <v>96520</v>
+        <v>96521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127731</v>
       </c>
       <c r="B2" t="n">
-        <v>96521</v>
+        <v>96527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136127743</v>
       </c>
       <c r="B3" t="n">
-        <v>96521</v>
+        <v>96527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127731</v>
       </c>
       <c r="B2" t="n">
-        <v>96527</v>
+        <v>96528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136127743</v>
       </c>
       <c r="B3" t="n">
-        <v>96527</v>
+        <v>96528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127731</v>
       </c>
       <c r="B2" t="n">
-        <v>96528</v>
+        <v>96539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136127743</v>
       </c>
       <c r="B3" t="n">
-        <v>96528</v>
+        <v>96539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127731</v>
       </c>
       <c r="B2" t="n">
-        <v>96539</v>
+        <v>96552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136127743</v>
       </c>
       <c r="B3" t="n">
-        <v>96539</v>
+        <v>96552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127731</v>
       </c>
       <c r="B2" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136127743</v>
       </c>
       <c r="B3" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127731</v>
       </c>
       <c r="B2" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136127743</v>
       </c>
       <c r="B3" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22738-2026 artfynd.xlsx
+++ b/artfynd/A 22738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127731</v>
       </c>
       <c r="B2" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136127743</v>
       </c>
       <c r="B3" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
